--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>100.2569086830617</v>
+        <v>16.29174766099753</v>
       </c>
       <c r="D2" t="n">
-        <v>6.131730761074278</v>
+        <v>0.9964062486745703</v>
       </c>
       <c r="E2" t="n">
-        <v>40.63790999716565</v>
+        <v>6.603660374539417</v>
       </c>
       <c r="F2" t="n">
-        <v>5.863629831382535</v>
+        <v>0.9528398475996619</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.15048934372885</v>
+        <v>2.136954518355938</v>
       </c>
       <c r="D3" t="n">
-        <v>2.978012184484466</v>
+        <v>0.4839269799787257</v>
       </c>
       <c r="E3" t="n">
-        <v>40.63790999716565</v>
+        <v>6.603660374539417</v>
       </c>
       <c r="F3" t="n">
-        <v>5.863629831382535</v>
+        <v>0.9528398475996619</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.98041339696727</v>
+        <v>2.434317177007181</v>
       </c>
       <c r="D4" t="n">
-        <v>16.68995453604724</v>
+        <v>2.712117612107676</v>
       </c>
       <c r="E4" t="n">
-        <v>40.63790999716565</v>
+        <v>6.603660374539417</v>
       </c>
       <c r="F4" t="n">
-        <v>5.863629831382535</v>
+        <v>0.9528398475996619</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
